--- a/LAPTOP DISTRIBUTION.xlsx
+++ b/LAPTOP DISTRIBUTION.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyProject\SLTSERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F76D2063-E4F1-4FE1-B3FF-DE9B6B2067B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F42D38F-B6C0-4ABB-8932-55DFBA92A8C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="2220" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1674,7 +1674,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1735,6 +1734,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2034,27 +2034,27 @@
     <col min="15" max="15" width="25.6640625" customWidth="1"/>
     <col min="16" max="16" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="15.5546875" customWidth="1"/>
-    <col min="18" max="18" width="10.109375" customWidth="1"/>
+    <col min="18" max="18" width="22.88671875" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="25.33203125" customWidth="1"/>
     <col min="20" max="20" width="26.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="C1" s="50" t="s">
+      <c r="C1" s="49" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="K1" s="52" t="s">
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="K1" s="51" t="s">
         <v>49</v>
       </c>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="51" t="s">
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="50" t="s">
         <v>149</v>
       </c>
-      <c r="O1" s="51"/>
-      <c r="P1" s="51"/>
+      <c r="O1" s="50"/>
+      <c r="P1" s="50"/>
     </row>
     <row r="2" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -2691,46 +2691,46 @@
       <c r="P15" s="5"/>
       <c r="Q15" s="5"/>
     </row>
-    <row r="16" spans="1:18" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="17">
+    <row r="16" spans="1:18" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="16">
         <v>14</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="E16" s="19">
+      <c r="E16" s="18">
         <v>7677</v>
       </c>
-      <c r="F16" s="19" t="s">
+      <c r="F16" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="19" t="s">
+      <c r="G16" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="H16" s="19" t="s">
+      <c r="H16" s="18" t="s">
         <v>55</v>
       </c>
       <c r="I16" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="J16" s="19" t="s">
+      <c r="J16" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="K16" s="19" t="s">
+      <c r="K16" s="18" t="s">
         <v>251</v>
       </c>
-      <c r="L16" s="19"/>
-      <c r="M16" s="20"/>
-      <c r="N16" s="19"/>
-      <c r="O16" s="19"/>
-      <c r="P16" s="19"/>
-      <c r="Q16" s="19"/>
+      <c r="L16" s="18"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="18"/>
+      <c r="O16" s="18"/>
+      <c r="P16" s="18"/>
+      <c r="Q16" s="18"/>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17">
@@ -3203,56 +3203,56 @@
         <v>66</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="17">
+    <row r="27" spans="1:17" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="16">
         <v>25</v>
       </c>
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="C27" s="19" t="s">
+      <c r="C27" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="D27" s="19" t="s">
+      <c r="D27" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="E27" s="19">
+      <c r="E27" s="18">
         <v>475</v>
       </c>
-      <c r="F27" s="19" t="s">
+      <c r="F27" s="18" t="s">
         <v>239</v>
       </c>
-      <c r="G27" s="19" t="s">
+      <c r="G27" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="H27" s="19" t="s">
+      <c r="H27" s="18" t="s">
         <v>55</v>
       </c>
       <c r="I27" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="J27" s="19" t="s">
+      <c r="J27" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="K27" s="19" t="s">
+      <c r="K27" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="L27" s="19" t="s">
+      <c r="L27" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="M27" s="20" t="s">
+      <c r="M27" s="19" t="s">
         <v>240</v>
       </c>
-      <c r="N27" s="19" t="s">
+      <c r="N27" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="O27" s="19" t="s">
+      <c r="O27" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="P27" s="19">
+      <c r="P27" s="18">
         <v>1344</v>
       </c>
-      <c r="Q27" s="19" t="s">
+      <c r="Q27" s="18" t="s">
         <v>88</v>
       </c>
     </row>
@@ -3819,50 +3819,50 @@
         <v>204</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="26" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="26">
+    <row r="40" spans="1:18" s="25" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="25">
         <v>38</v>
       </c>
-      <c r="B40" s="27" t="s">
+      <c r="B40" s="26" t="s">
         <v>205</v>
       </c>
-      <c r="C40" s="28" t="s">
+      <c r="C40" s="27" t="s">
         <v>206</v>
       </c>
-      <c r="D40" s="28" t="s">
+      <c r="D40" s="27" t="s">
         <v>123</v>
       </c>
-      <c r="E40" s="28">
+      <c r="E40" s="27">
         <v>7561</v>
       </c>
-      <c r="F40" s="28" t="s">
+      <c r="F40" s="27" t="s">
         <v>207</v>
       </c>
-      <c r="G40" s="28" t="s">
+      <c r="G40" s="27" t="s">
         <v>208</v>
       </c>
-      <c r="H40" s="28" t="s">
-        <v>55</v>
-      </c>
-      <c r="I40" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="J40" s="28" t="s">
+      <c r="H40" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="I40" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="J40" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="K40" s="28" t="s">
+      <c r="K40" s="27" t="s">
         <v>151</v>
       </c>
-      <c r="L40" s="28" t="s">
+      <c r="L40" s="27" t="s">
         <v>209</v>
       </c>
-      <c r="M40" s="29"/>
-      <c r="N40" s="28" t="s">
+      <c r="M40" s="28"/>
+      <c r="N40" s="27" t="s">
         <v>140</v>
       </c>
-      <c r="O40" s="28"/>
-      <c r="P40" s="28"/>
-      <c r="Q40" s="28"/>
+      <c r="O40" s="27"/>
+      <c r="P40" s="27"/>
+      <c r="Q40" s="27"/>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41">
@@ -4014,7 +4014,7 @@
       <c r="D44" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="E44" s="21">
+      <c r="E44" s="20">
         <v>7481</v>
       </c>
       <c r="F44" s="5" t="s">
@@ -4132,52 +4132,52 @@
       <c r="P46" s="5"/>
       <c r="Q46" s="5"/>
     </row>
-    <row r="47" spans="1:18" s="26" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="26">
+    <row r="47" spans="1:18" s="25" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="25">
         <v>45</v>
       </c>
-      <c r="B47" s="30">
+      <c r="B47" s="29">
         <v>45940</v>
       </c>
-      <c r="C47" s="31" t="s">
+      <c r="C47" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="D47" s="31" t="s">
+      <c r="D47" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="E47" s="31">
+      <c r="E47" s="30">
         <v>1328</v>
       </c>
-      <c r="F47" s="31" t="s">
+      <c r="F47" s="30" t="s">
         <v>254</v>
       </c>
-      <c r="G47" s="31" t="s">
+      <c r="G47" s="30" t="s">
         <v>125</v>
       </c>
-      <c r="H47" s="31" t="s">
-        <v>55</v>
-      </c>
-      <c r="I47" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="J47" s="31" t="s">
+      <c r="H47" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="I47" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="J47" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="K47" s="31" t="s">
+      <c r="K47" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="L47" s="31"/>
-      <c r="M47" s="32"/>
-      <c r="N47" s="31"/>
-      <c r="O47" s="31"/>
-      <c r="P47" s="31"/>
-      <c r="Q47" s="31"/>
+      <c r="L47" s="30"/>
+      <c r="M47" s="31"/>
+      <c r="N47" s="30"/>
+      <c r="O47" s="30"/>
+      <c r="P47" s="30"/>
+      <c r="Q47" s="30"/>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>46</v>
       </c>
-      <c r="B48" s="23" t="s">
+      <c r="B48" s="22" t="s">
         <v>260</v>
       </c>
       <c r="C48" s="5" t="s">
@@ -4204,7 +4204,7 @@
       <c r="J48" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="K48" s="22" t="s">
+      <c r="K48" s="21" t="s">
         <v>251</v>
       </c>
       <c r="L48" s="5"/>
@@ -4218,7 +4218,7 @@
       <c r="A49">
         <v>47</v>
       </c>
-      <c r="B49" s="23" t="s">
+      <c r="B49" s="22" t="s">
         <v>262</v>
       </c>
       <c r="C49" s="5" t="s">
@@ -4245,7 +4245,7 @@
       <c r="J49" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="K49" s="22" t="s">
+      <c r="K49" s="21" t="s">
         <v>251</v>
       </c>
       <c r="L49" s="5"/>
@@ -4259,7 +4259,7 @@
       <c r="A50">
         <v>48</v>
       </c>
-      <c r="B50" s="23">
+      <c r="B50" s="22">
         <v>45758</v>
       </c>
       <c r="C50" s="5" t="s">
@@ -4286,7 +4286,7 @@
       <c r="J50" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="K50" s="22" t="s">
+      <c r="K50" s="21" t="s">
         <v>251</v>
       </c>
       <c r="L50" s="5"/>
@@ -4300,7 +4300,7 @@
       <c r="A51">
         <v>49</v>
       </c>
-      <c r="B51" s="23">
+      <c r="B51" s="22">
         <v>45758</v>
       </c>
       <c r="C51" s="5" t="s">
@@ -4327,7 +4327,7 @@
       <c r="J51" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="K51" s="22" t="s">
+      <c r="K51" s="21" t="s">
         <v>145</v>
       </c>
       <c r="L51" s="5" t="s">
@@ -4345,7 +4345,7 @@
       <c r="A52">
         <v>50</v>
       </c>
-      <c r="B52" s="23">
+      <c r="B52" s="22">
         <v>45849</v>
       </c>
       <c r="C52" s="5" t="s">
@@ -4390,7 +4390,7 @@
       <c r="A53">
         <v>51</v>
       </c>
-      <c r="B53" s="24" t="s">
+      <c r="B53" s="23" t="s">
         <v>281</v>
       </c>
       <c r="C53" s="5" t="s">
@@ -4431,7 +4431,7 @@
       <c r="A54">
         <v>52</v>
       </c>
-      <c r="B54" s="24" t="s">
+      <c r="B54" s="23" t="s">
         <v>281</v>
       </c>
       <c r="C54" s="5" t="s">
@@ -4472,7 +4472,7 @@
       <c r="A55">
         <v>53</v>
       </c>
-      <c r="B55" s="24" t="s">
+      <c r="B55" s="23" t="s">
         <v>288</v>
       </c>
       <c r="C55" s="5" t="s">
@@ -4509,11 +4509,11 @@
       <c r="P55" s="5"/>
       <c r="Q55" s="5"/>
     </row>
-    <row r="56" spans="1:19" s="48" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="48">
+    <row r="56" spans="1:19" s="47" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="47">
         <v>54</v>
       </c>
-      <c r="B56" s="49" t="s">
+      <c r="B56" s="48" t="s">
         <v>438</v>
       </c>
       <c r="C56" s="9" t="s">
@@ -4681,7 +4681,7 @@
       <c r="N59" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="O59" s="25" t="s">
+      <c r="O59" s="24" t="s">
         <v>312</v>
       </c>
       <c r="P59" s="5">
@@ -4695,31 +4695,31 @@
       <c r="A60">
         <v>58</v>
       </c>
-      <c r="B60" s="33">
+      <c r="B60" s="32">
         <v>46063</v>
       </c>
-      <c r="C60" s="22" t="s">
+      <c r="C60" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="D60" s="22" t="s">
+      <c r="D60" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="E60" s="22">
+      <c r="E60" s="21">
         <v>721</v>
       </c>
-      <c r="F60" s="34" t="s">
+      <c r="F60" s="33" t="s">
         <v>314</v>
       </c>
-      <c r="G60" s="22" t="s">
+      <c r="G60" s="21" t="s">
         <v>315</v>
       </c>
-      <c r="H60" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="I60" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="J60" s="22" t="s">
+      <c r="H60" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="I60" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="J60" s="21" t="s">
         <v>316</v>
       </c>
       <c r="K60" t="s">
@@ -4727,21 +4727,21 @@
       </c>
     </row>
     <row r="61" spans="1:19" ht="15" x14ac:dyDescent="0.35">
-      <c r="B61" s="43"/>
-      <c r="C61" s="22"/>
-      <c r="D61" s="22"/>
-      <c r="E61" s="22"/>
-      <c r="F61" s="34"/>
-      <c r="G61" s="22">
+      <c r="B61" s="42"/>
+      <c r="C61" s="21"/>
+      <c r="D61" s="21"/>
+      <c r="E61" s="21"/>
+      <c r="F61" s="33"/>
+      <c r="G61" s="21">
         <v>2026</v>
       </c>
-      <c r="H61" s="22"/>
-      <c r="I61" s="35"/>
-      <c r="J61" s="22"/>
-      <c r="O61" s="42" t="s">
+      <c r="H61" s="21"/>
+      <c r="I61" s="34"/>
+      <c r="J61" s="21"/>
+      <c r="O61" s="41" t="s">
         <v>400</v>
       </c>
-      <c r="S61" s="42" t="s">
+      <c r="S61" s="41" t="s">
         <v>401</v>
       </c>
     </row>
@@ -4773,79 +4773,79 @@
       <c r="J62" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="K62" s="42" t="s">
+      <c r="K62" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="L62" s="42" t="s">
+      <c r="L62" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="M62" s="41" t="s">
+      <c r="M62" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="N62" s="41" t="s">
+      <c r="N62" s="40" t="s">
         <v>356</v>
       </c>
-      <c r="O62" s="41" t="s">
+      <c r="O62" s="40" t="s">
         <v>357</v>
       </c>
-      <c r="P62" s="41" t="s">
+      <c r="P62" s="40" t="s">
         <v>359</v>
       </c>
       <c r="Q62" s="5"/>
-      <c r="R62" s="41" t="s">
+      <c r="R62" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="S62" s="41" t="s">
+      <c r="S62" s="40" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="63" spans="1:19" ht="15" x14ac:dyDescent="0.35">
-      <c r="A63" s="42">
+      <c r="A63" s="41">
         <v>1</v>
       </c>
-      <c r="B63" s="36" t="s">
+      <c r="B63" s="35" t="s">
         <v>318</v>
       </c>
-      <c r="C63" s="37" t="s">
+      <c r="C63" s="36" t="s">
         <v>150</v>
       </c>
-      <c r="D63" s="37" t="s">
+      <c r="D63" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="E63" s="37">
+      <c r="E63" s="36">
         <v>600</v>
       </c>
-      <c r="F63" s="38" t="s">
+      <c r="F63" s="37" t="s">
         <v>319</v>
       </c>
-      <c r="G63" s="37" t="s">
+      <c r="G63" s="36" t="s">
         <v>369</v>
       </c>
-      <c r="H63" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="I63" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="J63" s="37" t="s">
+      <c r="H63" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="I63" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="J63" s="36" t="s">
         <v>320</v>
       </c>
-      <c r="K63" s="37" t="s">
+      <c r="K63" s="36" t="s">
         <v>145</v>
       </c>
-      <c r="L63" s="40" t="s">
+      <c r="L63" s="39" t="s">
         <v>321</v>
       </c>
-      <c r="M63" s="44" t="s">
+      <c r="M63" s="43" t="s">
         <v>422</v>
       </c>
-      <c r="N63" s="44">
+      <c r="N63" s="43">
         <v>928</v>
       </c>
-      <c r="O63" s="44" t="s">
+      <c r="O63" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="P63" s="44" t="s">
+      <c r="P63" s="43" t="s">
         <v>361</v>
       </c>
       <c r="Q63" s="5"/>
@@ -4853,52 +4853,52 @@
       <c r="S63" s="5"/>
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A64" s="42">
+      <c r="A64" s="41">
         <v>2</v>
       </c>
-      <c r="B64" s="37" t="s">
+      <c r="B64" s="36" t="s">
         <v>318</v>
       </c>
-      <c r="C64" s="37" t="s">
+      <c r="C64" s="36" t="s">
         <v>150</v>
       </c>
-      <c r="D64" s="37" t="s">
+      <c r="D64" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="E64" s="37">
+      <c r="E64" s="36">
         <v>532</v>
       </c>
-      <c r="F64" s="37" t="s">
+      <c r="F64" s="36" t="s">
         <v>322</v>
       </c>
-      <c r="G64" s="37" t="s">
+      <c r="G64" s="36" t="s">
         <v>370</v>
       </c>
-      <c r="H64" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="I64" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="J64" s="37" t="s">
+      <c r="H64" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="I64" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="J64" s="36" t="s">
         <v>323</v>
       </c>
-      <c r="K64" s="37" t="s">
+      <c r="K64" s="36" t="s">
         <v>145</v>
       </c>
-      <c r="L64" s="40" t="s">
+      <c r="L64" s="39" t="s">
         <v>420</v>
       </c>
-      <c r="M64" s="44" t="s">
+      <c r="M64" s="43" t="s">
         <v>421</v>
       </c>
-      <c r="N64" s="44">
+      <c r="N64" s="43">
         <v>1805</v>
       </c>
-      <c r="O64" s="44" t="s">
+      <c r="O64" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="P64" s="44" t="s">
+      <c r="P64" s="43" t="s">
         <v>361</v>
       </c>
       <c r="Q64" s="5"/>
@@ -4906,40 +4906,40 @@
       <c r="S64" s="5"/>
     </row>
     <row r="65" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A65" s="42">
+      <c r="A65" s="41">
         <v>3</v>
       </c>
-      <c r="B65" s="37" t="s">
+      <c r="B65" s="36" t="s">
         <v>318</v>
       </c>
-      <c r="C65" s="37" t="s">
+      <c r="C65" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="D65" s="37" t="s">
+      <c r="D65" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="E65" s="37">
+      <c r="E65" s="36">
         <v>608</v>
       </c>
-      <c r="F65" s="37" t="s">
+      <c r="F65" s="36" t="s">
         <v>324</v>
       </c>
-      <c r="G65" s="37" t="s">
+      <c r="G65" s="36" t="s">
         <v>371</v>
       </c>
-      <c r="H65" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="I65" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="J65" s="37" t="s">
+      <c r="H65" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="I65" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="J65" s="36" t="s">
         <v>325</v>
       </c>
-      <c r="K65" s="37" t="s">
+      <c r="K65" s="36" t="s">
         <v>145</v>
       </c>
-      <c r="L65" s="40" t="s">
+      <c r="L65" s="39" t="s">
         <v>335</v>
       </c>
       <c r="M65" s="5"/>
@@ -4951,40 +4951,40 @@
       <c r="S65" s="5"/>
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A66" s="42">
+      <c r="A66" s="41">
         <v>4</v>
       </c>
-      <c r="B66" s="37" t="s">
+      <c r="B66" s="36" t="s">
         <v>336</v>
       </c>
-      <c r="C66" s="37" t="s">
+      <c r="C66" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="D66" s="37" t="s">
+      <c r="D66" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="E66" s="37">
+      <c r="E66" s="36">
         <v>1133</v>
       </c>
-      <c r="F66" s="37" t="s">
+      <c r="F66" s="36" t="s">
         <v>337</v>
       </c>
-      <c r="G66" s="37" t="s">
+      <c r="G66" s="36" t="s">
         <v>372</v>
       </c>
-      <c r="H66" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="I66" s="28" t="s">
+      <c r="H66" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="I66" s="27" t="s">
         <v>293</v>
       </c>
-      <c r="J66" s="37" t="s">
+      <c r="J66" s="36" t="s">
         <v>326</v>
       </c>
-      <c r="K66" s="37" t="s">
+      <c r="K66" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="L66" s="40"/>
+      <c r="L66" s="39"/>
       <c r="M66" s="5"/>
       <c r="N66" s="5"/>
       <c r="O66" s="5"/>
@@ -4994,108 +4994,108 @@
       <c r="S66" s="5"/>
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A67" s="42">
+      <c r="A67" s="41">
         <v>5</v>
       </c>
-      <c r="B67" s="37" t="s">
+      <c r="B67" s="36" t="s">
         <v>336</v>
       </c>
-      <c r="C67" s="37" t="s">
+      <c r="C67" s="36" t="s">
         <v>150</v>
       </c>
-      <c r="D67" s="37" t="s">
+      <c r="D67" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="E67" s="37">
+      <c r="E67" s="36">
         <v>596</v>
       </c>
-      <c r="F67" s="37" t="s">
+      <c r="F67" s="36" t="s">
         <v>338</v>
       </c>
-      <c r="G67" s="37" t="s">
+      <c r="G67" s="36" t="s">
         <v>373</v>
       </c>
-      <c r="H67" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="I67" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="J67" s="37" t="s">
+      <c r="H67" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="I67" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="J67" s="36" t="s">
         <v>327</v>
       </c>
-      <c r="K67" s="37" t="s">
+      <c r="K67" s="36" t="s">
         <v>145</v>
       </c>
-      <c r="L67" s="40" t="s">
+      <c r="L67" s="39" t="s">
         <v>339</v>
       </c>
-      <c r="M67" s="44" t="s">
+      <c r="M67" s="43" t="s">
         <v>407</v>
       </c>
-      <c r="N67" s="44">
+      <c r="N67" s="43">
         <v>1326</v>
       </c>
-      <c r="O67" s="44" t="s">
+      <c r="O67" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="P67" s="44" t="s">
+      <c r="P67" s="43" t="s">
         <v>361</v>
       </c>
-      <c r="Q67" s="44"/>
+      <c r="Q67" s="43"/>
       <c r="R67" s="5"/>
       <c r="S67" s="5"/>
     </row>
     <row r="68" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A68" s="42">
+      <c r="A68" s="41">
         <v>6</v>
       </c>
-      <c r="B68" s="37" t="s">
+      <c r="B68" s="36" t="s">
         <v>336</v>
       </c>
-      <c r="C68" s="37" t="s">
+      <c r="C68" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="D68" s="37" t="s">
+      <c r="D68" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="E68" s="37">
+      <c r="E68" s="36">
         <v>604</v>
       </c>
-      <c r="F68" s="37" t="s">
+      <c r="F68" s="36" t="s">
         <v>340</v>
       </c>
-      <c r="G68" s="37" t="s">
+      <c r="G68" s="36" t="s">
         <v>374</v>
       </c>
-      <c r="H68" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="I68" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="J68" s="37" t="s">
+      <c r="H68" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="I68" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="J68" s="36" t="s">
         <v>328</v>
       </c>
-      <c r="K68" s="37" t="s">
+      <c r="K68" s="36" t="s">
         <v>145</v>
       </c>
-      <c r="L68" s="40" t="s">
+      <c r="L68" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="M68" s="44" t="s">
+      <c r="M68" s="43" t="s">
         <v>402</v>
       </c>
-      <c r="N68" s="44">
+      <c r="N68" s="43">
         <v>1267</v>
       </c>
-      <c r="O68" s="44" t="s">
+      <c r="O68" s="43" t="s">
         <v>403</v>
       </c>
-      <c r="P68" s="44" t="s">
+      <c r="P68" s="43" t="s">
         <v>361</v>
       </c>
-      <c r="Q68" s="44"/>
+      <c r="Q68" s="43"/>
       <c r="R68" s="9" t="s">
         <v>419</v>
       </c>
@@ -5104,220 +5104,220 @@
       </c>
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A69" s="42">
+      <c r="A69" s="41">
         <v>7</v>
       </c>
-      <c r="B69" s="37" t="s">
+      <c r="B69" s="36" t="s">
         <v>342</v>
       </c>
-      <c r="C69" s="37" t="s">
+      <c r="C69" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="D69" s="37" t="s">
+      <c r="D69" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="E69" s="37">
+      <c r="E69" s="36">
         <v>616</v>
       </c>
-      <c r="F69" s="37" t="s">
+      <c r="F69" s="36" t="s">
         <v>343</v>
       </c>
-      <c r="G69" s="37" t="s">
+      <c r="G69" s="36" t="s">
         <v>375</v>
       </c>
-      <c r="H69" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="I69" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="J69" s="37" t="s">
+      <c r="H69" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="I69" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="J69" s="36" t="s">
         <v>329</v>
       </c>
-      <c r="K69" s="37" t="s">
+      <c r="K69" s="36" t="s">
         <v>145</v>
       </c>
-      <c r="L69" s="40" t="s">
+      <c r="L69" s="39" t="s">
         <v>382</v>
       </c>
-      <c r="M69" s="44" t="s">
+      <c r="M69" s="43" t="s">
         <v>409</v>
       </c>
-      <c r="N69" s="44">
+      <c r="N69" s="43">
         <v>1195</v>
       </c>
-      <c r="O69" s="44" t="s">
+      <c r="O69" s="43" t="s">
         <v>417</v>
       </c>
-      <c r="P69" s="44" t="s">
+      <c r="P69" s="43" t="s">
         <v>361</v>
       </c>
-      <c r="Q69" s="44" t="s">
+      <c r="Q69" s="43" t="s">
         <v>362</v>
       </c>
       <c r="R69" s="5"/>
       <c r="S69" s="5"/>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A70" s="42">
+      <c r="A70" s="41">
         <v>8</v>
       </c>
-      <c r="B70" s="37" t="s">
+      <c r="B70" s="36" t="s">
         <v>344</v>
       </c>
-      <c r="C70" s="37" t="s">
+      <c r="C70" s="36" t="s">
         <v>97</v>
       </c>
-      <c r="D70" s="37" t="s">
+      <c r="D70" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="E70" s="37">
+      <c r="E70" s="36">
         <v>522</v>
       </c>
-      <c r="F70" s="37" t="s">
+      <c r="F70" s="36" t="s">
         <v>345</v>
       </c>
-      <c r="G70" s="37" t="s">
+      <c r="G70" s="36" t="s">
         <v>376</v>
       </c>
-      <c r="H70" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="I70" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="J70" s="37" t="s">
+      <c r="H70" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="I70" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="J70" s="36" t="s">
         <v>330</v>
       </c>
-      <c r="K70" s="37" t="s">
+      <c r="K70" s="36" t="s">
         <v>145</v>
       </c>
-      <c r="L70" s="40" t="s">
+      <c r="L70" s="39" t="s">
         <v>346</v>
       </c>
-      <c r="M70" s="45" t="s">
+      <c r="M70" s="44" t="s">
         <v>358</v>
       </c>
-      <c r="N70" s="44">
+      <c r="N70" s="43">
         <v>1724</v>
       </c>
-      <c r="O70" s="44" t="s">
+      <c r="O70" s="43" t="s">
         <v>360</v>
       </c>
-      <c r="P70" s="44" t="s">
+      <c r="P70" s="43" t="s">
         <v>361</v>
       </c>
-      <c r="Q70" s="44" t="s">
+      <c r="Q70" s="43" t="s">
         <v>362</v>
       </c>
       <c r="R70" s="5"/>
       <c r="S70" s="5"/>
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A71" s="42">
+      <c r="A71" s="41">
         <v>9</v>
       </c>
-      <c r="B71" s="37" t="s">
+      <c r="B71" s="36" t="s">
         <v>344</v>
       </c>
-      <c r="C71" s="37" t="s">
+      <c r="C71" s="36" t="s">
         <v>97</v>
       </c>
-      <c r="D71" s="37" t="s">
+      <c r="D71" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="E71" s="37">
+      <c r="E71" s="36">
         <v>620</v>
       </c>
-      <c r="F71" s="37" t="s">
+      <c r="F71" s="36" t="s">
         <v>347</v>
       </c>
-      <c r="G71" s="37" t="s">
+      <c r="G71" s="36" t="s">
         <v>377</v>
       </c>
-      <c r="H71" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="I71" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="J71" s="37" t="s">
+      <c r="H71" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="I71" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="J71" s="36" t="s">
         <v>331</v>
       </c>
-      <c r="K71" s="37" t="s">
+      <c r="K71" s="36" t="s">
         <v>145</v>
       </c>
-      <c r="L71" s="40" t="s">
+      <c r="L71" s="39" t="s">
         <v>348</v>
       </c>
-      <c r="M71" s="45" t="s">
+      <c r="M71" s="44" t="s">
         <v>363</v>
       </c>
-      <c r="N71" s="44">
+      <c r="N71" s="43">
         <v>1312</v>
       </c>
-      <c r="O71" s="44" t="s">
+      <c r="O71" s="43" t="s">
         <v>178</v>
       </c>
-      <c r="P71" s="44" t="s">
+      <c r="P71" s="43" t="s">
         <v>361</v>
       </c>
-      <c r="Q71" s="44" t="s">
+      <c r="Q71" s="43" t="s">
         <v>362</v>
       </c>
       <c r="R71" s="5"/>
       <c r="S71" s="5"/>
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A72" s="42">
+      <c r="A72" s="41">
         <v>10</v>
       </c>
-      <c r="B72" s="37" t="s">
+      <c r="B72" s="36" t="s">
         <v>344</v>
       </c>
-      <c r="C72" s="37" t="s">
+      <c r="C72" s="36" t="s">
         <v>206</v>
       </c>
-      <c r="D72" s="37" t="s">
+      <c r="D72" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="E72" s="37">
+      <c r="E72" s="36">
         <v>671</v>
       </c>
-      <c r="F72" s="37" t="s">
+      <c r="F72" s="36" t="s">
         <v>349</v>
       </c>
-      <c r="G72" s="37" t="s">
+      <c r="G72" s="36" t="s">
         <v>378</v>
       </c>
-      <c r="H72" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="I72" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="J72" s="37" t="s">
+      <c r="H72" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="I72" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="J72" s="36" t="s">
         <v>332</v>
       </c>
-      <c r="K72" s="37" t="s">
+      <c r="K72" s="36" t="s">
         <v>145</v>
       </c>
-      <c r="L72" s="40" t="s">
+      <c r="L72" s="39" t="s">
         <v>352</v>
       </c>
-      <c r="M72" s="44" t="s">
+      <c r="M72" s="43" t="s">
         <v>364</v>
       </c>
-      <c r="N72" s="44">
+      <c r="N72" s="43">
         <v>791</v>
       </c>
-      <c r="O72" s="44" t="s">
+      <c r="O72" s="43" t="s">
         <v>146</v>
       </c>
-      <c r="P72" s="44" t="s">
+      <c r="P72" s="43" t="s">
         <v>365</v>
       </c>
-      <c r="Q72" s="44"/>
+      <c r="Q72" s="43"/>
       <c r="R72" s="9" t="s">
         <v>381</v>
       </c>
@@ -5326,307 +5326,307 @@
       </c>
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A73" s="42">
+      <c r="A73" s="41">
         <v>11</v>
       </c>
-      <c r="B73" s="37" t="s">
+      <c r="B73" s="36" t="s">
         <v>344</v>
       </c>
-      <c r="C73" s="37" t="s">
+      <c r="C73" s="36" t="s">
         <v>350</v>
       </c>
-      <c r="D73" s="39" t="s">
+      <c r="D73" s="38" t="s">
         <v>123</v>
       </c>
-      <c r="E73" s="37">
+      <c r="E73" s="36">
         <v>387</v>
       </c>
-      <c r="F73" s="37" t="s">
+      <c r="F73" s="36" t="s">
         <v>351</v>
       </c>
       <c r="G73" s="9" t="s">
         <v>379</v>
       </c>
-      <c r="H73" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="I73" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="J73" s="37" t="s">
+      <c r="H73" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="I73" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="J73" s="36" t="s">
         <v>333</v>
       </c>
-      <c r="K73" s="37" t="s">
+      <c r="K73" s="36" t="s">
         <v>145</v>
       </c>
-      <c r="L73" s="40" t="s">
+      <c r="L73" s="39" t="s">
         <v>404</v>
       </c>
-      <c r="M73" s="44" t="s">
+      <c r="M73" s="43" t="s">
         <v>405</v>
       </c>
-      <c r="N73" s="44">
+      <c r="N73" s="43">
         <v>717</v>
       </c>
-      <c r="O73" s="44" t="s">
+      <c r="O73" s="43" t="s">
         <v>406</v>
       </c>
-      <c r="P73" s="46" t="s">
+      <c r="P73" s="45" t="s">
         <v>361</v>
       </c>
-      <c r="Q73" s="44" t="s">
+      <c r="Q73" s="43" t="s">
         <v>362</v>
       </c>
       <c r="R73" s="5"/>
       <c r="S73" s="5"/>
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A74" s="42">
+      <c r="A74" s="41">
         <v>12</v>
       </c>
-      <c r="B74" s="37" t="s">
+      <c r="B74" s="36" t="s">
         <v>353</v>
       </c>
-      <c r="C74" s="37" t="s">
+      <c r="C74" s="36" t="s">
         <v>97</v>
       </c>
-      <c r="D74" s="37" t="s">
+      <c r="D74" s="36" t="s">
         <v>136</v>
       </c>
-      <c r="E74" s="37">
+      <c r="E74" s="36">
         <v>493</v>
       </c>
-      <c r="F74" s="37" t="s">
+      <c r="F74" s="36" t="s">
         <v>354</v>
       </c>
-      <c r="G74" s="37" t="s">
+      <c r="G74" s="36" t="s">
         <v>380</v>
       </c>
-      <c r="H74" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="I74" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="J74" s="37" t="s">
+      <c r="H74" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="I74" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="J74" s="36" t="s">
         <v>334</v>
       </c>
-      <c r="K74" s="37" t="s">
+      <c r="K74" s="36" t="s">
         <v>145</v>
       </c>
-      <c r="L74" s="40" t="s">
+      <c r="L74" s="39" t="s">
         <v>355</v>
       </c>
-      <c r="M74" s="44" t="s">
+      <c r="M74" s="43" t="s">
         <v>418</v>
       </c>
-      <c r="N74" s="44">
+      <c r="N74" s="43">
         <v>1802</v>
       </c>
-      <c r="O74" s="44" t="s">
+      <c r="O74" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="P74" s="44" t="s">
+      <c r="P74" s="43" t="s">
         <v>361</v>
       </c>
-      <c r="Q74" s="44"/>
+      <c r="Q74" s="43"/>
       <c r="R74" s="5"/>
       <c r="S74" s="5"/>
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A75" s="42">
+      <c r="A75" s="41">
         <v>13</v>
       </c>
-      <c r="B75" s="37" t="s">
+      <c r="B75" s="36" t="s">
         <v>366</v>
       </c>
-      <c r="C75" s="37" t="s">
+      <c r="C75" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="D75" s="37" t="s">
+      <c r="D75" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="E75" s="37">
+      <c r="E75" s="36">
         <v>1041</v>
       </c>
-      <c r="F75" s="37" t="s">
+      <c r="F75" s="36" t="s">
         <v>243</v>
       </c>
-      <c r="G75" s="37" t="s">
+      <c r="G75" s="36" t="s">
         <v>367</v>
       </c>
-      <c r="H75" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="I75" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="J75" s="37" t="s">
+      <c r="H75" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="I75" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="J75" s="36" t="s">
         <v>368</v>
       </c>
-      <c r="K75" s="37" t="s">
+      <c r="K75" s="36" t="s">
         <v>145</v>
       </c>
-      <c r="L75" s="40" t="s">
+      <c r="L75" s="39" t="s">
         <v>244</v>
       </c>
-      <c r="M75" s="44" t="s">
+      <c r="M75" s="43" t="s">
         <v>408</v>
       </c>
-      <c r="N75" s="44">
+      <c r="N75" s="43">
         <v>1130</v>
       </c>
-      <c r="O75" s="44" t="s">
+      <c r="O75" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="P75" s="44" t="s">
+      <c r="P75" s="43" t="s">
         <v>361</v>
       </c>
-      <c r="Q75" s="44"/>
+      <c r="Q75" s="43"/>
       <c r="R75" s="5"/>
       <c r="S75" s="5"/>
     </row>
     <row r="76" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A76" s="42">
+      <c r="A76" s="41">
         <v>14</v>
       </c>
-      <c r="B76" s="37" t="s">
+      <c r="B76" s="36" t="s">
         <v>383</v>
       </c>
-      <c r="C76" s="37" t="s">
+      <c r="C76" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="D76" s="37" t="s">
+      <c r="D76" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="E76" s="37">
+      <c r="E76" s="36">
         <v>1184</v>
       </c>
-      <c r="F76" s="37" t="s">
+      <c r="F76" s="36" t="s">
         <v>410</v>
       </c>
-      <c r="G76" s="37" t="s">
+      <c r="G76" s="36" t="s">
         <v>384</v>
       </c>
-      <c r="H76" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="I76" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="J76" s="37" t="s">
+      <c r="H76" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="I76" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="J76" s="36" t="s">
         <v>385</v>
       </c>
-      <c r="K76" s="37" t="s">
+      <c r="K76" s="36" t="s">
         <v>145</v>
       </c>
-      <c r="L76" s="40" t="s">
+      <c r="L76" s="39" t="s">
         <v>411</v>
       </c>
-      <c r="M76" s="47" t="s">
+      <c r="M76" s="46" t="s">
         <v>415</v>
       </c>
-      <c r="N76" s="47">
+      <c r="N76" s="46">
         <v>844</v>
       </c>
-      <c r="O76" s="47" t="s">
+      <c r="O76" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="P76" s="47" t="s">
+      <c r="P76" s="46" t="s">
         <v>361</v>
       </c>
-      <c r="Q76" s="47"/>
+      <c r="Q76" s="46"/>
       <c r="R76" s="5"/>
       <c r="S76" s="5"/>
     </row>
     <row r="77" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A77" s="42">
+      <c r="A77" s="41">
         <v>15</v>
       </c>
-      <c r="B77" s="37" t="s">
+      <c r="B77" s="36" t="s">
         <v>383</v>
       </c>
-      <c r="C77" s="37" t="s">
+      <c r="C77" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="D77" s="37" t="s">
+      <c r="D77" s="36" t="s">
         <v>393</v>
       </c>
-      <c r="E77" s="37">
+      <c r="E77" s="36">
         <v>418</v>
       </c>
-      <c r="F77" s="37" t="s">
+      <c r="F77" s="36" t="s">
         <v>389</v>
       </c>
-      <c r="G77" s="37" t="s">
+      <c r="G77" s="36" t="s">
         <v>390</v>
       </c>
-      <c r="H77" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="I77" s="28" t="s">
+      <c r="H77" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="I77" s="27" t="s">
         <v>293</v>
       </c>
-      <c r="J77" s="37" t="s">
+      <c r="J77" s="36" t="s">
         <v>386</v>
       </c>
-      <c r="K77" s="37" t="s">
+      <c r="K77" s="36" t="s">
         <v>145</v>
       </c>
-      <c r="L77" s="40" t="s">
+      <c r="L77" s="39" t="s">
         <v>413</v>
       </c>
-      <c r="M77" s="47" t="s">
+      <c r="M77" s="46" t="s">
         <v>414</v>
       </c>
-      <c r="N77" s="47">
+      <c r="N77" s="46">
         <v>519</v>
       </c>
-      <c r="O77" s="47" t="s">
+      <c r="O77" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="P77" s="47" t="s">
+      <c r="P77" s="46" t="s">
         <v>361</v>
       </c>
-      <c r="Q77" s="47"/>
+      <c r="Q77" s="46"/>
       <c r="R77" s="5"/>
       <c r="S77" s="5"/>
     </row>
     <row r="78" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A78" s="42">
+      <c r="A78" s="41">
         <v>16</v>
       </c>
-      <c r="B78" s="37" t="s">
+      <c r="B78" s="36" t="s">
         <v>383</v>
       </c>
-      <c r="C78" s="37" t="s">
+      <c r="C78" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="D78" s="37" t="s">
+      <c r="D78" s="36" t="s">
         <v>82</v>
       </c>
-      <c r="E78" s="37">
+      <c r="E78" s="36">
         <v>451</v>
       </c>
-      <c r="F78" s="37" t="s">
+      <c r="F78" s="36" t="s">
         <v>391</v>
       </c>
-      <c r="G78" s="37" t="s">
+      <c r="G78" s="36" t="s">
         <v>392</v>
       </c>
-      <c r="H78" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="I78" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="J78" s="37" t="s">
+      <c r="H78" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="I78" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="J78" s="36" t="s">
         <v>387</v>
       </c>
-      <c r="K78" s="37" t="s">
+      <c r="K78" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="L78" s="40"/>
+      <c r="L78" s="39"/>
       <c r="M78" s="5"/>
       <c r="N78" s="5"/>
       <c r="O78" s="5"/>
@@ -5636,91 +5636,91 @@
       <c r="S78" s="5"/>
     </row>
     <row r="79" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A79" s="42">
+      <c r="A79" s="41">
         <v>17</v>
       </c>
-      <c r="B79" s="37" t="s">
+      <c r="B79" s="36" t="s">
         <v>383</v>
       </c>
-      <c r="C79" s="37" t="s">
+      <c r="C79" s="36" t="s">
         <v>394</v>
       </c>
-      <c r="D79" s="37" t="s">
+      <c r="D79" s="36" t="s">
         <v>82</v>
       </c>
-      <c r="E79" s="37">
+      <c r="E79" s="36">
         <v>1040</v>
       </c>
-      <c r="F79" s="37" t="s">
+      <c r="F79" s="36" t="s">
         <v>395</v>
       </c>
-      <c r="G79" s="37" t="s">
+      <c r="G79" s="36" t="s">
         <v>396</v>
       </c>
-      <c r="H79" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="I79" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="J79" s="37" t="s">
+      <c r="H79" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="I79" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="J79" s="36" t="s">
         <v>388</v>
       </c>
-      <c r="K79" s="37" t="s">
+      <c r="K79" s="36" t="s">
         <v>145</v>
       </c>
-      <c r="L79" s="40" t="s">
+      <c r="L79" s="39" t="s">
         <v>412</v>
       </c>
-      <c r="M79" s="44" t="s">
+      <c r="M79" s="43" t="s">
         <v>416</v>
       </c>
-      <c r="N79" s="44">
+      <c r="N79" s="43">
         <v>1831</v>
       </c>
-      <c r="O79" s="44" t="s">
+      <c r="O79" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="P79" s="44"/>
-      <c r="Q79" s="44"/>
+      <c r="P79" s="43"/>
+      <c r="Q79" s="43"/>
       <c r="R79" s="5"/>
       <c r="S79" s="5"/>
     </row>
     <row r="80" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A80" s="42">
+      <c r="A80" s="41">
         <v>18</v>
       </c>
-      <c r="B80" s="37" t="s">
+      <c r="B80" s="36" t="s">
         <v>383</v>
       </c>
-      <c r="C80" s="37" t="s">
+      <c r="C80" s="36" t="s">
         <v>394</v>
       </c>
-      <c r="D80" s="37" t="s">
+      <c r="D80" s="36" t="s">
         <v>278</v>
       </c>
-      <c r="E80" s="37">
+      <c r="E80" s="36">
         <v>540</v>
       </c>
-      <c r="F80" s="37" t="s">
+      <c r="F80" s="36" t="s">
         <v>397</v>
       </c>
-      <c r="G80" s="37" t="s">
+      <c r="G80" s="36" t="s">
         <v>398</v>
       </c>
-      <c r="H80" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="I80" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="J80" s="37" t="s">
+      <c r="H80" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="I80" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="J80" s="36" t="s">
         <v>399</v>
       </c>
-      <c r="K80" s="37" t="s">
+      <c r="K80" s="36" t="s">
         <v>145</v>
       </c>
-      <c r="L80" s="40" t="s">
+      <c r="L80" s="39" t="s">
         <v>166</v>
       </c>
       <c r="M80" s="5"/>
@@ -5732,36 +5732,36 @@
       <c r="S80" s="5"/>
     </row>
     <row r="81" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A81" s="42">
+      <c r="A81" s="41">
         <v>1</v>
       </c>
-      <c r="B81" s="37" t="s">
+      <c r="B81" s="36" t="s">
         <v>423</v>
       </c>
-      <c r="C81" s="37" t="s">
+      <c r="C81" s="36" t="s">
         <v>350</v>
       </c>
-      <c r="D81" s="37" t="s">
+      <c r="D81" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="E81" s="37"/>
-      <c r="F81" s="37" t="s">
+      <c r="E81" s="36"/>
+      <c r="F81" s="36" t="s">
         <v>425</v>
       </c>
-      <c r="G81" s="37" t="s">
+      <c r="G81" s="36" t="s">
         <v>424</v>
       </c>
-      <c r="H81" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="I81" s="28" t="s">
+      <c r="H81" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="I81" s="27" t="s">
         <v>293</v>
       </c>
-      <c r="J81" s="37" t="s">
+      <c r="J81" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="K81" s="37"/>
-      <c r="L81" s="40"/>
+      <c r="K81" s="36"/>
+      <c r="L81" s="39"/>
       <c r="M81" s="5"/>
       <c r="N81" s="5"/>
       <c r="O81" s="5"/>
@@ -5771,40 +5771,40 @@
       <c r="S81" s="5"/>
     </row>
     <row r="82" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A82" s="42">
+      <c r="A82" s="41">
         <v>2</v>
       </c>
-      <c r="B82" s="37" t="s">
+      <c r="B82" s="36" t="s">
         <v>423</v>
       </c>
-      <c r="C82" s="37" t="s">
+      <c r="C82" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="D82" s="37" t="s">
+      <c r="D82" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="E82" s="37">
+      <c r="E82" s="36">
         <v>387</v>
       </c>
-      <c r="F82" s="37" t="s">
+      <c r="F82" s="36" t="s">
         <v>351</v>
       </c>
-      <c r="G82" s="37" t="s">
+      <c r="G82" s="36" t="s">
         <v>426</v>
       </c>
-      <c r="H82" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="I82" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="J82" s="37" t="s">
+      <c r="H82" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="I82" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="J82" s="36" t="s">
         <v>427</v>
       </c>
-      <c r="K82" s="37" t="s">
+      <c r="K82" s="36" t="s">
         <v>145</v>
       </c>
-      <c r="L82" s="40" t="s">
+      <c r="L82" s="39" t="s">
         <v>379</v>
       </c>
       <c r="M82" s="5" t="s">
@@ -5824,40 +5824,40 @@
       <c r="S82" s="5"/>
     </row>
     <row r="83" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A83" s="42">
+      <c r="A83" s="41">
         <v>3</v>
       </c>
-      <c r="B83" s="37" t="s">
+      <c r="B83" s="36" t="s">
         <v>444</v>
       </c>
-      <c r="C83" s="37" t="s">
+      <c r="C83" s="36" t="s">
         <v>97</v>
       </c>
-      <c r="D83" s="37" t="s">
+      <c r="D83" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="E83" s="37">
+      <c r="E83" s="36">
         <v>522</v>
       </c>
-      <c r="F83" s="37" t="s">
+      <c r="F83" s="36" t="s">
         <v>345</v>
       </c>
-      <c r="G83" s="37" t="s">
+      <c r="G83" s="36" t="s">
         <v>441</v>
       </c>
-      <c r="H83" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="I83" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="J83" s="37" t="s">
+      <c r="H83" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="I83" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="J83" s="36" t="s">
         <v>428</v>
       </c>
-      <c r="K83" s="37" t="s">
+      <c r="K83" s="36" t="s">
         <v>145</v>
       </c>
-      <c r="L83" s="40" t="s">
+      <c r="L83" s="39" t="s">
         <v>376</v>
       </c>
       <c r="M83" s="5" t="s">
@@ -5881,40 +5881,40 @@
       </c>
     </row>
     <row r="84" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A84" s="42">
+      <c r="A84" s="41">
         <v>4</v>
       </c>
-      <c r="B84" s="37" t="s">
+      <c r="B84" s="36" t="s">
         <v>444</v>
       </c>
-      <c r="C84" s="37" t="s">
+      <c r="C84" s="36" t="s">
         <v>97</v>
       </c>
-      <c r="D84" s="37" t="s">
+      <c r="D84" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="E84" s="37">
+      <c r="E84" s="36">
         <v>620</v>
       </c>
-      <c r="F84" s="37" t="s">
+      <c r="F84" s="36" t="s">
         <v>347</v>
       </c>
-      <c r="G84" s="37" t="s">
+      <c r="G84" s="36" t="s">
         <v>445</v>
       </c>
-      <c r="H84" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="I84" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="J84" s="37" t="s">
+      <c r="H84" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="I84" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="J84" s="36" t="s">
         <v>429</v>
       </c>
-      <c r="K84" s="37" t="s">
+      <c r="K84" s="36" t="s">
         <v>145</v>
       </c>
-      <c r="L84" s="40" t="s">
+      <c r="L84" s="39" t="s">
         <v>446</v>
       </c>
       <c r="M84" s="5"/>
@@ -5926,40 +5926,40 @@
       <c r="S84" s="5"/>
     </row>
     <row r="85" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A85" s="42">
+      <c r="A85" s="41">
         <v>5</v>
       </c>
-      <c r="B85" s="37" t="s">
+      <c r="B85" s="36" t="s">
         <v>447</v>
       </c>
-      <c r="C85" s="37" t="s">
+      <c r="C85" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="D85" s="37" t="s">
+      <c r="D85" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="E85" s="37">
+      <c r="E85" s="36">
         <v>608</v>
       </c>
-      <c r="F85" s="37" t="s">
+      <c r="F85" s="36" t="s">
         <v>324</v>
       </c>
-      <c r="G85" s="37" t="s">
+      <c r="G85" s="36" t="s">
         <v>448</v>
       </c>
-      <c r="H85" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="I85" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="J85" s="37" t="s">
+      <c r="H85" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="I85" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="J85" s="36" t="s">
         <v>430</v>
       </c>
-      <c r="K85" s="37" t="s">
+      <c r="K85" s="36" t="s">
         <v>145</v>
       </c>
-      <c r="L85" s="40" t="s">
+      <c r="L85" s="39" t="s">
         <v>371</v>
       </c>
       <c r="M85" s="5" t="s">
@@ -5979,40 +5979,40 @@
       <c r="S85" s="5"/>
     </row>
     <row r="86" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A86" s="42">
+      <c r="A86" s="41">
         <v>6</v>
       </c>
-      <c r="B86" s="37" t="s">
+      <c r="B86" s="36" t="s">
         <v>447</v>
       </c>
-      <c r="C86" s="37" t="s">
+      <c r="C86" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="D86" s="37" t="s">
+      <c r="D86" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="E86" s="37">
+      <c r="E86" s="36">
         <v>671</v>
       </c>
-      <c r="F86" s="37" t="s">
+      <c r="F86" s="36" t="s">
         <v>349</v>
       </c>
-      <c r="G86" s="37" t="s">
+      <c r="G86" s="36" t="s">
         <v>449</v>
       </c>
-      <c r="H86" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="I86" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="J86" s="37" t="s">
+      <c r="H86" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="I86" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="J86" s="36" t="s">
         <v>431</v>
       </c>
-      <c r="K86" s="37" t="s">
+      <c r="K86" s="36" t="s">
         <v>145</v>
       </c>
-      <c r="L86" s="40" t="s">
+      <c r="L86" s="39" t="s">
         <v>378</v>
       </c>
       <c r="M86" s="5" t="s">
@@ -6036,40 +6036,40 @@
       </c>
     </row>
     <row r="87" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A87" s="42">
+      <c r="A87" s="41">
         <v>7</v>
       </c>
-      <c r="B87" s="37" t="s">
+      <c r="B87" s="36" t="s">
         <v>451</v>
       </c>
-      <c r="C87" s="37" t="s">
+      <c r="C87" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="D87" s="37" t="s">
+      <c r="D87" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="E87" s="37">
+      <c r="E87" s="36">
         <v>1133</v>
       </c>
-      <c r="F87" s="37" t="s">
+      <c r="F87" s="36" t="s">
         <v>337</v>
       </c>
-      <c r="G87" s="37" t="s">
+      <c r="G87" s="36" t="s">
         <v>452</v>
       </c>
-      <c r="H87" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="I87" s="28" t="s">
+      <c r="H87" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="I87" s="27" t="s">
         <v>293</v>
       </c>
-      <c r="J87" s="37" t="s">
+      <c r="J87" s="36" t="s">
         <v>432</v>
       </c>
-      <c r="K87" s="37" t="s">
+      <c r="K87" s="36" t="s">
         <v>145</v>
       </c>
-      <c r="L87" s="40" t="s">
+      <c r="L87" s="39" t="s">
         <v>453</v>
       </c>
       <c r="M87" s="5"/>
@@ -6081,40 +6081,40 @@
       <c r="S87" s="5"/>
     </row>
     <row r="88" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A88" s="42">
+      <c r="A88" s="41">
         <v>8</v>
       </c>
-      <c r="B88" s="37" t="s">
+      <c r="B88" s="36" t="s">
         <v>451</v>
       </c>
-      <c r="C88" s="37" t="s">
+      <c r="C88" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="D88" s="37" t="s">
+      <c r="D88" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="E88" s="37">
+      <c r="E88" s="36">
         <v>453</v>
       </c>
-      <c r="F88" s="37" t="s">
+      <c r="F88" s="36" t="s">
         <v>454</v>
       </c>
-      <c r="G88" s="37" t="s">
+      <c r="G88" s="36" t="s">
         <v>455</v>
       </c>
-      <c r="H88" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="I88" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="J88" s="37" t="s">
+      <c r="H88" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="I88" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="J88" s="36" t="s">
         <v>433</v>
       </c>
-      <c r="K88" s="37" t="s">
+      <c r="K88" s="36" t="s">
         <v>145</v>
       </c>
-      <c r="L88" s="40" t="s">
+      <c r="L88" s="39" t="s">
         <v>456</v>
       </c>
       <c r="M88" s="5" t="s">
@@ -6134,22 +6134,22 @@
       <c r="S88" s="5"/>
     </row>
     <row r="89" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A89" s="42">
+      <c r="A89" s="41">
         <v>9</v>
       </c>
-      <c r="B89" s="37"/>
-      <c r="C89" s="37"/>
-      <c r="D89" s="37"/>
-      <c r="E89" s="37"/>
-      <c r="F89" s="37"/>
-      <c r="G89" s="37"/>
-      <c r="H89" s="37"/>
-      <c r="I89" s="37"/>
-      <c r="J89" s="37" t="s">
+      <c r="B89" s="36"/>
+      <c r="C89" s="36"/>
+      <c r="D89" s="36"/>
+      <c r="E89" s="36"/>
+      <c r="F89" s="36"/>
+      <c r="G89" s="36"/>
+      <c r="H89" s="36"/>
+      <c r="I89" s="36"/>
+      <c r="J89" s="36" t="s">
         <v>434</v>
       </c>
-      <c r="K89" s="37"/>
-      <c r="L89" s="40"/>
+      <c r="K89" s="36"/>
+      <c r="L89" s="39"/>
       <c r="M89" s="5"/>
       <c r="N89" s="5"/>
       <c r="O89" s="5"/>
@@ -6159,22 +6159,22 @@
       <c r="S89" s="5"/>
     </row>
     <row r="90" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A90" s="42">
+      <c r="A90" s="41">
         <v>10</v>
       </c>
-      <c r="B90" s="37"/>
-      <c r="C90" s="37"/>
-      <c r="D90" s="37"/>
-      <c r="E90" s="37"/>
-      <c r="F90" s="37"/>
-      <c r="G90" s="37"/>
-      <c r="H90" s="37"/>
-      <c r="I90" s="37"/>
-      <c r="J90" s="37" t="s">
+      <c r="B90" s="36"/>
+      <c r="C90" s="36"/>
+      <c r="D90" s="36"/>
+      <c r="E90" s="36"/>
+      <c r="F90" s="36"/>
+      <c r="G90" s="36"/>
+      <c r="H90" s="36"/>
+      <c r="I90" s="36"/>
+      <c r="J90" s="36" t="s">
         <v>435</v>
       </c>
-      <c r="K90" s="37"/>
-      <c r="L90" s="40"/>
+      <c r="K90" s="36"/>
+      <c r="L90" s="39"/>
       <c r="M90" s="5"/>
       <c r="N90" s="5"/>
       <c r="O90" s="5"/>
@@ -6184,22 +6184,22 @@
       <c r="S90" s="5"/>
     </row>
     <row r="91" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A91" s="42">
+      <c r="A91" s="41">
         <v>11</v>
       </c>
-      <c r="B91" s="37"/>
-      <c r="C91" s="37"/>
-      <c r="D91" s="37"/>
-      <c r="E91" s="37"/>
-      <c r="F91" s="37"/>
-      <c r="G91" s="37"/>
-      <c r="H91" s="37"/>
-      <c r="I91" s="37"/>
-      <c r="J91" s="37" t="s">
+      <c r="B91" s="36"/>
+      <c r="C91" s="36"/>
+      <c r="D91" s="36"/>
+      <c r="E91" s="36"/>
+      <c r="F91" s="36"/>
+      <c r="G91" s="36"/>
+      <c r="H91" s="36"/>
+      <c r="I91" s="36"/>
+      <c r="J91" s="36" t="s">
         <v>436</v>
       </c>
-      <c r="K91" s="37"/>
-      <c r="L91" s="40"/>
+      <c r="K91" s="36"/>
+      <c r="L91" s="39"/>
       <c r="M91" s="5"/>
       <c r="N91" s="5"/>
       <c r="O91" s="5"/>
@@ -6209,22 +6209,22 @@
       <c r="S91" s="5"/>
     </row>
     <row r="92" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A92" s="42">
+      <c r="A92" s="41">
         <v>12</v>
       </c>
-      <c r="B92" s="37"/>
-      <c r="C92" s="37"/>
-      <c r="D92" s="37"/>
-      <c r="E92" s="37"/>
-      <c r="F92" s="37"/>
-      <c r="G92" s="37"/>
-      <c r="H92" s="37"/>
-      <c r="I92" s="37"/>
-      <c r="J92" s="37" t="s">
+      <c r="B92" s="36"/>
+      <c r="C92" s="36"/>
+      <c r="D92" s="36"/>
+      <c r="E92" s="36"/>
+      <c r="F92" s="36"/>
+      <c r="G92" s="36"/>
+      <c r="H92" s="36"/>
+      <c r="I92" s="36"/>
+      <c r="J92" s="36" t="s">
         <v>437</v>
       </c>
-      <c r="K92" s="37"/>
-      <c r="L92" s="40"/>
+      <c r="K92" s="36"/>
+      <c r="L92" s="39"/>
       <c r="M92" s="5"/>
       <c r="N92" s="5"/>
       <c r="O92" s="5"/>
@@ -6233,61 +6233,61 @@
       <c r="R92" s="5"/>
       <c r="S92" s="5"/>
     </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A95">
+    <row r="95" spans="1:19" s="47" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="47">
         <v>1</v>
       </c>
-      <c r="D95" t="s">
+      <c r="D95" s="47" t="s">
         <v>123</v>
       </c>
-      <c r="E95">
+      <c r="E95" s="47">
         <v>618</v>
       </c>
-      <c r="F95" t="s">
+      <c r="F95" s="47" t="s">
         <v>184</v>
       </c>
-      <c r="G95" t="s">
+      <c r="G95" s="47" t="s">
         <v>183</v>
       </c>
-      <c r="L95" t="s">
+      <c r="L95" s="47" t="s">
         <v>183</v>
       </c>
-      <c r="N95" t="s">
+      <c r="N95" s="47" t="s">
         <v>141</v>
       </c>
-      <c r="O95" s="16" t="s">
+      <c r="O95" s="52" t="s">
         <v>185</v>
       </c>
-      <c r="P95" t="s">
+      <c r="P95" s="47" t="s">
         <v>186</v>
       </c>
-      <c r="Q95" t="s">
+      <c r="Q95" s="47" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A96">
+    <row r="96" spans="1:19" s="47" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="47">
         <v>2</v>
       </c>
-      <c r="D96" t="s">
+      <c r="D96" s="47" t="s">
         <v>133</v>
       </c>
-      <c r="E96">
+      <c r="E96" s="47">
         <v>995</v>
       </c>
-      <c r="L96" t="s">
+      <c r="L96" s="47" t="s">
         <v>215</v>
       </c>
-      <c r="N96" t="s">
+      <c r="N96" s="47" t="s">
         <v>140</v>
       </c>
-      <c r="O96" t="s">
+      <c r="O96" s="47" t="s">
         <v>216</v>
       </c>
-      <c r="P96">
+      <c r="P96" s="47">
         <v>995</v>
       </c>
-      <c r="Q96" t="s">
+      <c r="Q96" s="47" t="s">
         <v>122</v>
       </c>
     </row>
@@ -6508,7 +6508,7 @@
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" s="19" t="s">
+      <c r="A40" s="18" t="s">
         <v>101</v>
       </c>
     </row>
@@ -6563,7 +6563,7 @@
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" s="19" t="s">
+      <c r="A51" s="18" t="s">
         <v>130</v>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A64" s="28" t="s">
+      <c r="A64" s="27" t="s">
         <v>208</v>
       </c>
     </row>
@@ -6663,7 +6663,7 @@
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A71" s="31" t="s">
+      <c r="A71" s="30" t="s">
         <v>125</v>
       </c>
     </row>
@@ -6728,7 +6728,7 @@
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A84" s="22" t="s">
+      <c r="A84" s="21" t="s">
         <v>315</v>
       </c>
     </row>

--- a/LAPTOP DISTRIBUTION.xlsx
+++ b/LAPTOP DISTRIBUTION.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyProject\SLTSERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F42D38F-B6C0-4ABB-8932-55DFBA92A8C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD94068-141D-45CA-8DA7-828A048CBAAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="2220" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Computer" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Computer!$A$2:$Q$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Computer!$A$2:$Q$92</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="463">
   <si>
     <t>248/2025/CA/LAP/001</t>
   </si>
@@ -1439,6 +1439,9 @@
   </si>
   <si>
     <t>SAJITH KIRTHIRATHNE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Houseing Change </t>
   </si>
 </sst>
 </file>
@@ -1725,6 +1728,7 @@
     <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1734,7 +1738,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2040,21 +2043,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="C1" s="49" t="s">
+      <c r="C1" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="K1" s="51" t="s">
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="K1" s="52" t="s">
         <v>49</v>
       </c>
-      <c r="L1" s="51"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="50" t="s">
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="51" t="s">
         <v>149</v>
       </c>
-      <c r="O1" s="50"/>
-      <c r="P1" s="50"/>
+      <c r="O1" s="51"/>
+      <c r="P1" s="51"/>
     </row>
     <row r="2" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -3517,7 +3520,9 @@
       <c r="L33" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="M33" s="12"/>
+      <c r="M33" s="12" t="s">
+        <v>462</v>
+      </c>
       <c r="N33" s="5" t="s">
         <v>140</v>
       </c>
@@ -6255,7 +6260,7 @@
       <c r="N95" s="47" t="s">
         <v>141</v>
       </c>
-      <c r="O95" s="52" t="s">
+      <c r="O95" s="49" t="s">
         <v>185</v>
       </c>
       <c r="P95" s="47" t="s">
@@ -6292,7 +6297,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Q47" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:Q92" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="3">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="N1:P1"/>

--- a/LAPTOP DISTRIBUTION.xlsx
+++ b/LAPTOP DISTRIBUTION.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyProject\SLTSERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD94068-141D-45CA-8DA7-828A048CBAAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A91432C0-BB4F-4376-8220-0443A22FC91A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
